--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_7.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9997115776624154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7113361178117402</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996020836758962</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9999034560220054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997963273531844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.125633654139209</v>
+        <v>0.0001712199587864902</v>
       </c>
       <c r="H2" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1713633500973782</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01211937515414544</v>
+        <v>8.265750406317285e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006637054032799197</v>
+        <v>3.611663321912491e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009378214593240581</v>
+        <v>5.938706864114888e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.004199807847171232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.0130851044621925</v>
       </c>
       <c r="N2" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000203592238295</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.01364216444904842</v>
       </c>
       <c r="P2" t="n">
-        <v>156.1487702277424</v>
+        <v>133.3451230387099</v>
       </c>
       <c r="Q2" t="n">
-        <v>248.7833329177256</v>
+        <v>204.0399208810655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_22</t>
+          <t>model_25_7_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9997605443172082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7100205121101894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996670677942816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.999868462781733</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997970271237987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.125633654139209</v>
+        <v>0.0001421512372521331</v>
       </c>
       <c r="H3" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1721443504730259</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01211937515414544</v>
+        <v>6.915862325805846e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006637054032799197</v>
+        <v>4.920743443028752e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009378214593240581</v>
+        <v>5.9183028844173e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.004004802368507964</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.01192271937320229</v>
       </c>
       <c r="N3" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000169027540794</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.01243029422035104</v>
       </c>
       <c r="P3" t="n">
-        <v>156.1487702277424</v>
+        <v>133.7172380321123</v>
       </c>
       <c r="Q3" t="n">
-        <v>248.7833329177256</v>
+        <v>204.412035874468</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_21</t>
+          <t>model_25_7_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9997989102369526</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7088405583266195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997144957365655</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.999830584304171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997896224137137</v>
       </c>
       <c r="G4" t="n">
-        <v>0.125633654139209</v>
+        <v>0.0001193755699704024</v>
       </c>
       <c r="H4" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1728448220103024</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.9306613942113e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006637054032799197</v>
+        <v>6.337758889690188e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009378214593240581</v>
+        <v>6.134210141950743e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003835542051399571</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.0109259127751599</v>
       </c>
       <c r="N4" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000141945715092</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.01139105150175587</v>
       </c>
       <c r="P4" t="n">
-        <v>156.1487702277424</v>
+        <v>134.0664719691072</v>
       </c>
       <c r="Q4" t="n">
-        <v>248.7833329177256</v>
+        <v>204.7612698114629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_20</t>
+          <t>model_25_7_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998287101147125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7077845187688762</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997471299606072</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9997907172311091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997756724179896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.125633654139209</v>
+        <v>0.0001016850752444326</v>
       </c>
       <c r="H5" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1734717327103124</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.252764222639132e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006637054032799197</v>
+        <v>7.829166728071282e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009378214593240581</v>
+        <v>6.540965475355207e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003688507803236229</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.0100839017867308</v>
       </c>
       <c r="N5" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000120910507262</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.01051319436234631</v>
       </c>
       <c r="P5" t="n">
-        <v>156.1487702277424</v>
+        <v>134.3872600368755</v>
       </c>
       <c r="Q5" t="n">
-        <v>248.7833329177256</v>
+        <v>205.0820578792312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_19</t>
+          <t>model_25_7_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.999851614589507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7068406018339002</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997675416053111</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9997497116353325</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997566383089506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.125633654139209</v>
+        <v>8.808798958459892e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1740320825780026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01211937515414544</v>
+        <v>4.828761611323699e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006637054032799197</v>
+        <v>9.363166148188696e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009378214593240581</v>
+        <v>7.095963879756198e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003560513705267388</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.009385520208523282</v>
       </c>
       <c r="N6" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000104742642701</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.009785081234505331</v>
       </c>
       <c r="P6" t="n">
-        <v>156.1487702277424</v>
+        <v>134.6743487227832</v>
       </c>
       <c r="Q6" t="n">
-        <v>248.7833329177256</v>
+        <v>205.3691465651388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_18</t>
+          <t>model_25_7_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998689803530949</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7059977490631422</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997780159452433</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9997082540691211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997337745348052</v>
       </c>
       <c r="G7" t="n">
-        <v>0.125633654139209</v>
+        <v>7.777892215692568e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1745324363920684</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01211937515414544</v>
+        <v>4.611182501580672e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0001091407356273189</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009378214593240581</v>
+        <v>7.762628032156283e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003448977956542395</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008819235916842551</v>
       </c>
       <c r="N7" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000092484456639</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.009194689048157666</v>
       </c>
       <c r="P7" t="n">
-        <v>156.1487702277424</v>
+        <v>134.9232801738383</v>
       </c>
       <c r="Q7" t="n">
-        <v>248.7833329177256</v>
+        <v>205.6180780161939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_17</t>
+          <t>model_25_7_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998819318080757</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7052452610582087</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997805938229229</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9996670015648952</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9997082308694828</v>
       </c>
       <c r="G8" t="n">
-        <v>0.125633654139209</v>
+        <v>7.009037900654499e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1749791457775862</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01211937515414544</v>
+        <v>4.557633320040315e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0001245730970800763</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009378214593240581</v>
+        <v>8.507432712393903e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003351627073804362</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008371999701776451</v>
       </c>
       <c r="N8" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000083342253123</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008728413061509607</v>
       </c>
       <c r="P8" t="n">
-        <v>156.1487702277424</v>
+        <v>135.1314500400797</v>
       </c>
       <c r="Q8" t="n">
-        <v>248.7833329177256</v>
+        <v>205.8262478824353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_16</t>
+          <t>model_25_7_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998913886276778</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7045734752278282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.99977706586404</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9996264904020272</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.99968098673585</v>
       </c>
       <c r="G9" t="n">
-        <v>0.125633654139209</v>
+        <v>6.447640237744045e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.374415341109035</v>
+        <v>0.175377946866137</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01211937515414544</v>
+        <v>4.630918143514913e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.000139728126331728</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009378214593240581</v>
+        <v>9.301819813172967e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003266351602700537</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008029719943898445</v>
       </c>
       <c r="N9" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000076666851051</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008371561745721958</v>
       </c>
       <c r="P9" t="n">
-        <v>156.1487702277424</v>
+        <v>135.298422511434</v>
       </c>
       <c r="Q9" t="n">
-        <v>248.7833329177256</v>
+        <v>205.9932203537896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_15</t>
+          <t>model_25_7_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998980793462019</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7039737571773041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997689112298889</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9995870619861195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9996527873330656</v>
       </c>
       <c r="G10" t="n">
-        <v>0.125633654139209</v>
+        <v>6.050450283752543e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1757339654073989</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01211937515414544</v>
+        <v>4.800310969254778e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.000154478105204914</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001012406074487309</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003191907618295315</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007778464041025415</v>
       </c>
       <c r="N10" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000071943990916</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008109609358892203</v>
       </c>
       <c r="P10" t="n">
-        <v>156.1487702277424</v>
+        <v>135.425585537261</v>
       </c>
       <c r="Q10" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1203833796166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_14</t>
+          <t>model_25_7_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999026105055927</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7034379474575748</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997573983528948</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9995490990488194</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9996243316325238</v>
       </c>
       <c r="G11" t="n">
-        <v>0.125633654139209</v>
+        <v>5.781461088724314e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.374415341109035</v>
+        <v>0.176052045202805</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.039463177714554e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0001686798556492804</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001095377483153657</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003126573857879177</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007603591972695743</v>
       </c>
       <c r="N11" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000068745525464</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.00792729262457865</v>
       </c>
       <c r="P11" t="n">
-        <v>156.1487702277424</v>
+        <v>135.516538061428</v>
       </c>
       <c r="Q11" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2113359037836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_13</t>
+          <t>model_25_7_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999054691576058</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7029592861228051</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997435224162996</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.99951283950669</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9995961303754</v>
       </c>
       <c r="G12" t="n">
-        <v>0.125633654139209</v>
+        <v>5.611759156497095e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1763361992482173</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.327702241062139e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0001822443742343162</v>
       </c>
       <c r="K12" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001177606983224688</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003069030877617683</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.00749116757021033</v>
       </c>
       <c r="N12" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000066727653455</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007810082082528837</v>
       </c>
       <c r="P12" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5761224389137</v>
       </c>
       <c r="Q12" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2709202812694</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_23</t>
+          <t>model_25_7_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999070447993353</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7025313474874458</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997281140292879</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9994784575442422</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9995685869030542</v>
       </c>
       <c r="G13" t="n">
-        <v>0.125633654139209</v>
+        <v>5.518222257011672e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.374415341109035</v>
+        <v>0.176590242108153</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.64777425994532e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0001951064993805104</v>
       </c>
       <c r="K13" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001257918508036138</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003018313738206498</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007428473771247814</v>
       </c>
       <c r="N13" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000065615435763</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007744719278750431</v>
       </c>
       <c r="P13" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6097394228825</v>
       </c>
       <c r="Q13" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3045372652381</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999076393619005</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7021486441735316</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9997118420106593</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9994459762603959</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9995419532213483</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125633654139209</v>
+        <v>5.482926454768742e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1768174313272148</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01211937515414544</v>
+        <v>5.985786139436814e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002072575898941833</v>
       </c>
       <c r="K14" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001335577256442757</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002980227590841167</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007404678558025826</v>
       </c>
       <c r="N14" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000065195744541</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007719911054038701</v>
       </c>
       <c r="P14" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6225729639157</v>
       </c>
       <c r="Q14" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3173708062713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_10</t>
+          <t>model_25_7_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999075118494748</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7018061171621404</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996952051050281</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9994155514903778</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9995165097334636</v>
       </c>
       <c r="G15" t="n">
-        <v>0.125633654139209</v>
+        <v>5.490496143180268e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1770207701575732</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01211937515414544</v>
+        <v>6.331377664968941e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002186393485739739</v>
       </c>
       <c r="K15" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001409765626118316</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002950573798783375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.00740978821774298</v>
       </c>
       <c r="N15" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000065285753312</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007725238242548468</v>
       </c>
       <c r="P15" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6198136827362</v>
       </c>
       <c r="Q15" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3146115250919</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_9</t>
+          <t>model_25_7_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999068522788028</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7014994637768599</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996786069909521</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9993871145441745</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9994923546399745</v>
       </c>
       <c r="G16" t="n">
-        <v>0.125633654139209</v>
+        <v>5.529651107468731e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772028128538121</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01211937515414544</v>
+        <v>6.67616338964693e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.000229277472020184</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001480197282872394</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002924656144564975</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007436162388940099</v>
       </c>
       <c r="N16" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00006575133261</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007752735216815509</v>
       </c>
       <c r="P16" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6056014845999</v>
       </c>
       <c r="Q16" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3003993269555</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_8</t>
+          <t>model_25_7_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.999905813103739</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7012249047021273</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996623205817963</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.999360674415243</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9994695904113499</v>
       </c>
       <c r="G17" t="n">
-        <v>0.125633654139209</v>
+        <v>5.59134102825695e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1773658029809079</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01211937515414544</v>
+        <v>7.014474197581361e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002391685958242629</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001546573442313996</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002901903771311698</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.00747752701650549</v>
       </c>
       <c r="N17" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000066484867949</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007795860822212944</v>
       </c>
       <c r="P17" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5834126177074</v>
       </c>
       <c r="Q17" t="n">
-        <v>248.7833329177256</v>
+        <v>206.278210460063</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_7</t>
+          <t>model_25_7_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999045193328091</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.700978813191051</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996465405290371</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9993362096431516</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9994482777612796</v>
       </c>
       <c r="G18" t="n">
-        <v>0.125633654139209</v>
+        <v>5.668144859460517e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1775118935324825</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01211937515414544</v>
+        <v>7.342266674552641e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002483207482295185</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001608717074875225</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002881991027560522</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007528708295226025</v>
       </c>
       <c r="N18" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000067398118017</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007849220993928464</v>
       </c>
       <c r="P18" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5561271720954</v>
       </c>
       <c r="Q18" t="n">
-        <v>248.7833329177256</v>
+        <v>206.250925014451</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_6</t>
+          <t>model_25_7_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999030587375746</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7007582359810935</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.999631476717606</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9993135620287475</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9994283836211785</v>
       </c>
       <c r="G19" t="n">
-        <v>0.125633654139209</v>
+        <v>5.754852102019515e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1776428376927526</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01211937515414544</v>
+        <v>7.655180968124542e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002567931107704808</v>
       </c>
       <c r="K19" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001666724602258631</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002864417153481178</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007586074150718219</v>
       </c>
       <c r="N19" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000068429126418</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007909029032652653</v>
       </c>
       <c r="P19" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5257642443351</v>
       </c>
       <c r="Q19" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2205620866907</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_5</t>
+          <t>model_25_7_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.999901505163719</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7005603948798558</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996171676407226</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992927192275994</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9994099160997845</v>
       </c>
       <c r="G20" t="n">
-        <v>0.125633654139209</v>
+        <v>5.847078957179711e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1777602847167379</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01211937515414544</v>
+        <v>7.952417474640619e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.00026459030143908</v>
       </c>
       <c r="K20" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001720572380927431</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.00284896883728803</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007646619486531098</v>
       </c>
       <c r="N20" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000069525766787</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007972151908757209</v>
       </c>
       <c r="P20" t="n">
-        <v>156.1487702277424</v>
+        <v>135.493966503978</v>
       </c>
       <c r="Q20" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1887643463336</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_4</t>
+          <t>model_25_7_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998999123226061</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7003829481666952</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9996036876176502</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992735714798215</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993928312597169</v>
       </c>
       <c r="G21" t="n">
-        <v>0.125633654139209</v>
+        <v>5.941636886356277e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1778656247509689</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01211937515414544</v>
+        <v>8.232432390940462e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002717533808752968</v>
       </c>
       <c r="K21" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001770388523923507</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002835312150140835</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007708201402633611</v>
       </c>
       <c r="N21" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000070650125219</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008036355494520345</v>
       </c>
       <c r="P21" t="n">
-        <v>156.1487702277424</v>
+        <v>135.461881598929</v>
       </c>
       <c r="Q21" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1566794412846</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_3</t>
+          <t>model_25_7_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998983208228275</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7002236012640296</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9995910548628228</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992560243911919</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993770750357004</v>
       </c>
       <c r="G22" t="n">
-        <v>0.125633654139209</v>
+        <v>6.036115188138681e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.374415341109035</v>
+        <v>0.177960219955819</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01211937515414544</v>
+        <v>8.494847356153302e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002783176614991474</v>
       </c>
       <c r="K22" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001816330675303402</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.0028230968890068</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007769243971030052</v>
       </c>
       <c r="N22" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000071773536828</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008099996771428961</v>
       </c>
       <c r="P22" t="n">
-        <v>156.1487702277424</v>
+        <v>135.4303296814495</v>
       </c>
       <c r="Q22" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1251275238051</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_2</t>
+          <t>model_25_7_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.999896759106003</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7000806624148368</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9995792906604454</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992399560326027</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993625767924545</v>
       </c>
       <c r="G23" t="n">
-        <v>0.125633654139209</v>
+        <v>6.128825445106754e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1780450746313367</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01211937515414544</v>
+        <v>8.739220242338313e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.000284328756397611</v>
       </c>
       <c r="K23" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001858604794104971</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002812436526795649</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007828681526992112</v>
       </c>
       <c r="N23" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000072875925174</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008161964707201028</v>
       </c>
       <c r="P23" t="n">
-        <v>156.1487702277424</v>
+        <v>135.399844682062</v>
       </c>
       <c r="Q23" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0946425244176</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_1</t>
+          <t>model_25_7_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998952509595216</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.6999523838919057</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9995684087548801</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992252868923543</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993492904194927</v>
       </c>
       <c r="G24" t="n">
-        <v>0.125633654139209</v>
+        <v>6.218355535090426e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1781212263038922</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01211937515414544</v>
+        <v>8.96526554357162e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002898164105112653</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001897345329734907</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.00280286979428456</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007885655036260732</v>
       </c>
       <c r="N24" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000073940499161</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008221363696710636</v>
       </c>
       <c r="P24" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3708399532011</v>
       </c>
       <c r="Q24" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0656377955568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_11</t>
+          <t>model_25_7_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998938064676014</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.6998372628098273</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9995582991434714</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9992119149936297</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993371113156372</v>
       </c>
       <c r="G25" t="n">
-        <v>0.125633654139209</v>
+        <v>6.3041068153538e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1781895671511858</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01211937515414544</v>
+        <v>9.175268299294903e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002948187728720199</v>
       </c>
       <c r="K25" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001932857279324845</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002794408089784933</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.00793984056222403</v>
       </c>
       <c r="N25" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000074960140517</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008277856012693693</v>
       </c>
       <c r="P25" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3434483369965</v>
       </c>
       <c r="Q25" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0382461793522</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998924384289342</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.6997337662544976</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9944016022794893</v>
+        <v>0.9995490436288337</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9987723714532359</v>
+        <v>0.9991997066105828</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9981855879620333</v>
+        <v>0.9993259828350923</v>
       </c>
       <c r="G26" t="n">
-        <v>0.125633654139209</v>
+        <v>6.385319500259472e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1782510071772479</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01211937515414544</v>
+        <v>9.367529257801798e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.006637054032799197</v>
+        <v>0.0002993858696694145</v>
       </c>
       <c r="K26" t="n">
-        <v>0.009378214593240581</v>
+        <v>0.0001965305811237162</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002786844435479909</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007990819419971566</v>
       </c>
       <c r="N26" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00007592581487</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008331005145956326</v>
       </c>
       <c r="P26" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3178478750855</v>
       </c>
       <c r="Q26" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0126457174411</v>
       </c>
     </row>
   </sheetData>
